--- a/Configs/GameConfig/Datas/Ball.xlsx
+++ b/Configs/GameConfig/Datas/Ball.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ball" sheetId="1" r:id="R9772a6555dc54d64"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ball" sheetId="1" r:id="Rec65a0cc68824ae3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -604,10 +604,8 @@
           <x:t xml:space="preserve">White</x:t>
         </x:is>
       </x:c>
-      <x:c r="D5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">BilliardsWhiteBall</x:t>
-        </x:is>
+      <x:c r="D5" t="str">
+        <x:v>WhiteBall</x:v>
       </x:c>
       <x:c r="E5" t="n">
         <x:v>1</x:v>
@@ -636,10 +634,8 @@
           <x:t xml:space="preserve">Black</x:t>
         </x:is>
       </x:c>
-      <x:c r="D6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">BilliardsBlackBall</x:t>
-        </x:is>
+      <x:c r="D6" t="str">
+        <x:v>BlackBall</x:v>
       </x:c>
       <x:c r="E6" t="n">
         <x:v>1</x:v>
@@ -661,10 +657,8 @@
           <x:t xml:space="preserve">White</x:t>
         </x:is>
       </x:c>
-      <x:c r="D7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">BilliardsWhiteBall</x:t>
-        </x:is>
+      <x:c r="D7" t="str">
+        <x:v>WhiteBall</x:v>
       </x:c>
       <x:c r="E7" t="n">
         <x:v>1</x:v>
